--- a/astro-site/public/dl/chocolate-shop-checklist-templates/02-chocolate-tempering-molding-checklists.xlsx
+++ b/astro-site/public/dl/chocolate-shop-checklist-templates/02-chocolate-tempering-molding-checklists.xlsx
@@ -866,7 +866,7 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>Check milk couverture stock (35–40% cocoa)</t>
+          <t>Check milk couverture stock (30–40% cocoa)</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
@@ -958,7 +958,7 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Tempering Process — Dark Chocolate</t>
+          <t>Tempering Process — Dark Chocolate (typical curve; your couverture's chart rules)</t>
         </is>
       </c>
     </row>
@@ -1097,7 +1097,7 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Tempering Process — Milk Chocolate</t>
+          <t>Tempering Process — Milk Chocolate (typical curve; your couverture's chart rules)</t>
         </is>
       </c>
     </row>
@@ -1217,7 +1217,7 @@
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>Tempering Process — White Chocolate</t>
+          <t>Tempering Process — White Chocolate (typical curve; your couverture's chart rules)</t>
         </is>
       </c>
     </row>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>Prep clean molds at room temperature (68–72 °F)</t>
+          <t>Prep clean molds, slightly warmer than the room (68–72 °F)</t>
         </is>
       </c>
       <c r="C6" s="14" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Chill at 54–57 °F for 10–15 min</t>
+          <t>Chill 10–15 min in a cooling cabinet or fridge set to 54–57 °F</t>
         </is>
       </c>
       <c r="C10" s="17" t="inlineStr">
         <is>
-          <t>Cool room</t>
+          <t>Fridge</t>
         </is>
       </c>
       <c r="D10" s="11" t="n"/>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>Fill bonbons to 80%, leaving room for the cap</t>
+          <t>Fill bonbons to 80%, leaving room for the cap; let the filling set before capping (ganache: usually overnight — if it is TCS, in the fridge)</t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="C14" s="17" t="inlineStr">
         <is>
-          <t>Cool room</t>
+          <t>Fridge</t>
         </is>
       </c>
       <c r="D14" s="11" t="n"/>
@@ -1719,7 +1719,7 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Prep clean bar molds at room temperature</t>
+          <t>Prep clean bar molds, slightly warmer than the room (68–72 °F)</t>
         </is>
       </c>
       <c r="C19" s="14" t="inlineStr">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>Add inclusions if needed: nuts, dried fruit, salt</t>
+          <t>Add inclusions if needed: nuts, dried fruit, salt — run nut and peanut bars LAST, then clean molds, tools and the tempering machine before plain bars (allergen cross-contact)</t>
         </is>
       </c>
       <c r="C21" s="14" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Chill at 54–57 °F for 20–30 min</t>
+          <t>Chill 20–30 min in a cooling cabinet or fridge set to 54–57 °F</t>
         </is>
       </c>
       <c r="C23" s="17" t="inlineStr">
         <is>
-          <t>Cool room</t>
+          <t>Fridge</t>
         </is>
       </c>
       <c r="D23" s="11" t="n"/>
@@ -1972,7 +1972,7 @@
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>Store finished product at 59–64 °F and 50–60% humidity, in the dark and away from strong odors (cocoa absorbs them) — log reading: ____ °F</t>
+          <t>Store finished product at 59–64 °F and 50–60% humidity, in the dark and away from strong odors (cocoa absorbs them); TCS fresh-cream items in the fridge at 41 °F or below — log reading: ____ °F</t>
         </is>
       </c>
       <c r="C33" s="17" t="inlineStr">
@@ -2085,7 +2085,7 @@
       <c r="F40" s="19" t="n"/>
       <c r="G40" s="20" t="n"/>
     </row>
-    <row r="41" ht="45" customHeight="1">
+    <row r="41" ht="75" customHeight="1">
       <c r="A41" s="8" t="n"/>
       <c r="B41" s="21" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="D41" s="23" t="inlineStr">
         <is>
-          <t>Treat it as TCS: 41 °F or below, 7 days max (FDA date marking). Let the box warm up CLOSED before opening, or it sweats. Longer only with a lab water-activity test</t>
+          <t>Treat it as TCS until a lab test (water activity and pH; FDA 1-201.10) shows it is not: 41 °F or below, 7 days max (date marking), so NOT in the 60–64 °F display case or the cool room — use a refrigerated case or the fridge. Let the box warm up CLOSED before opening, or it sweats</t>
         </is>
       </c>
       <c r="E41" s="19" t="n"/>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="D42" s="23" t="inlineStr">
         <is>
-          <t>Preservative and alcohol lower water activity; without them you will not reach even half of this. Only with a lab-tested water activity (not TCS); otherwise, treat it as fresh-cream ganache</t>
+          <t>Preservative and alcohol lower water activity; without them you will not reach even half of this. Only with a lab test of water activity and pH showing it is not TCS; otherwise, treat it as fresh-cream ganache</t>
         </is>
       </c>
       <c r="E42" s="19" t="n"/>
@@ -2148,7 +2148,7 @@
       <c r="F43" s="19" t="n"/>
       <c r="G43" s="20" t="n"/>
     </row>
-    <row r="44" ht="30" customHeight="1">
+    <row r="44" ht="45" customHeight="1">
       <c r="A44" s="8" t="n"/>
       <c r="B44" s="21" t="inlineStr">
         <is>
@@ -2162,14 +2162,14 @@
       </c>
       <c r="D44" s="23" t="inlineStr">
         <is>
-          <t>If they contain cream or butter, count them as fresh ganache</t>
+          <t>Truffles with fresh cream or butter follow the fresh-cream row (TCS unless lab-tested); nut or praline centers, this row</t>
         </is>
       </c>
       <c r="E44" s="19" t="n"/>
       <c r="F44" s="19" t="n"/>
       <c r="G44" s="20" t="n"/>
     </row>
-    <row r="45" ht="30" customHeight="1">
+    <row r="45" ht="60" customHeight="1">
       <c r="A45" s="8" t="n"/>
       <c r="B45" s="21" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
       </c>
       <c r="D45" s="23" t="inlineStr">
         <is>
-          <t>Watch for sugar crystallization in the shell: it cracks and leaks. Alcohol-filled candy: check your state rules</t>
+          <t>Watch for sugar crystallization in the shell: it cracks and leaks. Alcohol: above 0.5% only where state law allows; ship only to states that allow it (FD&amp;C Act §402(d)); some states set 21+ — check your state rules</t>
         </is>
       </c>
       <c r="E45" s="19" t="n"/>
